--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cfd_005/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cfd_005/extracted.xlsx
@@ -284,6 +284,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -559,11 +564,6 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="G7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
     <comment ref="H7" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -595,6 +595,11 @@
       </text>
     </comment>
     <comment ref="F8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="G8" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1361,12 +1366,12 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Steady RANS aerodynamic prediction of CRM wing-body at transonic cruise for pre-PDR design trades</t>
+          <t>Steady RANS prediction of cruise lift, drag, and pitching moment for NASA CRM wing-body at M=0.85</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>FUN3D 13.9 RANS simulations of the NASA Common Research Model wing-body configuration at M∞=0.85, Re=5e6/ft, α∈[-1,3] deg, used to inform early trade studies on cruise drag, lift, and pitching moment for a notional transport aircraft. Results are intended for concept evaluation and margin-setting, not for final certification.</t>
+          <t>FUN3D 13.9 RANS simulations of the NASA Common Research Model wing-body configuration at transonic cruise conditions (M∞=0.85, Re=5e6/ft, α=-1 to 3 deg) to support early trade studies on cruise drag and lift-to-drag ratio at pre-PDR level. Outputs are CL, CD, and CM trends with angle of attack.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1404,9 +1409,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md / appendix.md — CFD Credibility Assessment Report, Project: Transonic Wing-Body Aerodynamics (NASA CRM), dated 2026-08-06</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1525,7 +1530,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Pre-PDR Aerodynamic Accuracy Requirement</t>
+          <t>Aerodynamic Prediction Credibility for Pre-PDR Trade Studies</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1535,7 +1540,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Simulation results must reproduce CRM wind-tunnel lift slope, pitching moment trends, and drag levels to within a margin sufficient for concept ranking and margin-setting (drag bias recognized and bracketed to within ~8-9 counts); numerical uncertainty in drag must be below ~1.1 counts at 95% confidence for the fine mesh solution.</t>
+          <t>Simulation predictions of CL, CD, and CM must be credible for ranking design options and assessing drag margins at the level of a few drag counts in the specified transonic cruise operating window, with numerical uncertainty in drag bounded to approximately 1.1 counts at 95% confidence.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1557,29 +1562,29 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>FUN3D 13.9 SA-RC RANS Model</t>
+          <t>FUN3D 13.9 Steady RANS with SA-RC</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Steady compressible Reynolds-averaged Navier-Stokes solver with Spalart-Allmaras rotation/curvature correction turbulence closure, second-order finite volume discretization, Roe-Turkel flux, applied to CRM wing-body half-model on unstructured hybrid meshes.</t>
+          <t>Compressible steady RANS solver with Spalart-Allmaras rotation/curvature correction turbulence closure, second-order finite volume, Roe-Turkel flux, Venkatakrishnan limiter, GMRES/ILU(1) linear solver.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Dataset</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>NASA CRM Wind Tunnel Database</t>
+          <t>NASA CRM Wing-Body Mesh Family (Coarse/Medium/Fine)</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Publicly available CRM wing-body experimental dataset at M∞=0.85, Re=5e6/ft, α∈[-1,3] deg providing CL, CD, CM, and surface pressure tap data used for validation comparisons.</t>
+          <t>Three-level unstructured hybrid mesh family (8.6M, 17.2M, 34.5M cells) generated in Pointwise 18.5R2 with prismatic near-wall layers targeting y+&lt;1.</t>
         </is>
       </c>
     </row>
@@ -1591,29 +1596,29 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>NASA CRM v2.0 CAD Geometry</t>
+          <t>NASA CRM Public Wind Tunnel Database</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Reference CAD geometry for the CRM wing-body configuration used to generate computational meshes; gap healing and watertightness enforced via Pointwise Glyph script.</t>
+          <t>Publicly available wind-tunnel measurements for the CRM wing-body at M∞=0.85, Re=5e6/ft, α∈[-1,3] deg, including corrected CL, CD, and CM values used for validation comparisons.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Dataset</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Three-Level Hybrid Mesh Family</t>
+          <t>NASA CRM v2.0 CAD Geometry</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Coarse (8.6M cells), medium (17.2M cells), and fine (34.5M cells) unstructured prismatic/tetrahedral meshes generated in Pointwise 18.5R2 with refinement ratio r≈1.26, used for Richardson extrapolation and GCI estimation.</t>
+          <t>Public reference geometry for the CRM wing-body used to generate computational meshes; gaps healed and wing-fuselage watertightness enforced via Pointwise Glyph script.</t>
         </is>
       </c>
     </row>
@@ -2065,12 +2070,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Three-mesh family (coarse/medium/fine) run at α=2.0 deg, M∞=0.85. Monotonic convergence observed for CL (0.536→0.542→0.545) and CD (0.02891→0.02867→0.02857). Richardson extrapolation applied with observed order p≈1.95 (drag) and p≈2.08 (lift).</t>
+          <t>Three-level mesh refinement study (coarse 8.6M, medium 17.2M, fine 34.5M cells) at M∞=0.85, α=2.0 deg. CL and CD exhibit monotonic convergence. Richardson extrapolation performed with observed order p≈1.95 (drag) and p≈2.08 (lift).</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Richardson-extrapolated infinite-grid values; GCI methodology per Roache 1998</t>
+          <t>Richardson extrapolated infinite-grid values; expected second-order convergence rate</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2080,12 +2085,12 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Richardson extrapolation and Grid Convergence Index (95% coverage)</t>
+          <t>Richardson extrapolation, Grid Convergence Index (GCI) at 95% coverage</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>CD GCI = 0.8 counts (95%); CL GCI = 0.6%; estimated infinite-grid CD = 0.02852</t>
+          <t>GCI_drag=0.8 counts (95%); GCI_lift=0.6%; observed order p≈1.95–2.08</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2097,7 +2102,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Method of Manufactured Solutions — 2D Compressible Flow</t>
+          <t>Method of Manufactured Solutions (MMS) — 2D Compressible Field</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2107,12 +2112,12 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>2D compressible MMS with smooth trigonometric velocity/temperature fields and analytically derived body force run on uniform triangular meshes from 64² to 512². Observed convergence rates checked against expected second-order accuracy.</t>
+          <t>2D compressible manufactured solution with trigonometric velocity and temperature fields and analytically derived body force. L2 norm of velocity error measured on uniform triangular meshes from 64² to 512² cells.</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Analytical manufactured solution; expected L2 slope of 2.0</t>
+          <t>Analytical manufactured solution</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
@@ -2122,7 +2127,7 @@
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>L2(u) slope 1.98–2.01; L∞(p) slope 1.72–1.85</t>
+          <t>L2(u) slopes 1.98–2.01; L∞(p) slopes 1.72–1.85</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2134,7 +2139,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Laminar Flat-Plate Benchmark</t>
+          <t>Laminar Flat-Plate Skin-Friction Benchmark</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2144,12 +2149,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Laminar subsonic flat-plate simulation (domain 2 m, M=0.2, SA trip disabled) compared to Blasius analytical solution for skin-friction coefficient at Rex=1e6.</t>
+          <t>Laminar subsonic flat plate (domain 2 m, M=0.2, SA trip disabled) skin-friction coefficient compared to Blasius analytical solution at x=1.5 m (Rex=1e6), using wall y+≈0.9 and 30 prism layers.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Blasius analytical solution</t>
+          <t>Blasius analytical skin-friction solution</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -2159,7 +2164,7 @@
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>c_f within 1.7% of Blasius at x=1.5 m; wall y+≈0.9</t>
+          <t>c_f within 1.7% of Blasius at Rex=1e6</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2171,7 +2176,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>CRM Wind-Tunnel Comparison — Lift, Drag, Pitching Moment</t>
+          <t>CRM Wind-Tunnel Comparison — Lift, Drag, and Pitching Moment</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2181,12 +2186,12 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Fine-mesh RANS predictions at M∞=0.85, Re=5e6/ft, α∈[-1,3] deg compared to publicly available CRM wind-tunnel dataset. CL slope, CD, and CM at α=2.0 deg evaluated; surface pressure signatures compared qualitatively.</t>
+          <t>Fine-mesh RANS predictions compared to publicly available CRM wind-tunnel dataset at M∞=0.85, Re=5e6/ft, α∈[-1,3] deg. CL, CD, CM, and surface pressure signatures compared quantitatively.</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>NASA CRM wind tunnel database (M∞=0.85, Re=5e6/ft)</t>
+          <t>NASA CRM public wind tunnel database (corrected values)</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -2196,12 +2201,12 @@
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Quadrature combination of GCI, iterative noise, and far-field truncation contributions; 95% bound estimated</t>
+          <t>Quadrature combination of grid, iterative, and far-field truncation contributions to numerical uncertainty</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>CL offset 1.1% (0.545 vs 0.539); CD shortfall 8.5 counts (0.02857 vs 0.02942); CM offset 1.6%; CL slope 0.096 vs ~0.095/deg; numerical uncertainty in drag ~0.9-1.1 counts (95%)</t>
+          <t>CL error=1.1% at α=2 deg; CD underprediction=8.5 counts at α=2 deg; CM error=1.6%; CL-α slope 0.096 vs 0.095/deg; combined numerical 95% bound ~0.9–1.1 counts drag, ~0.7% lift</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2213,7 +2218,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Iterative Convergence and Restart Robustness Study</t>
+          <t>Far-Field Domain Size Sensitivity Study</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -2223,27 +2228,22 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Residuals monitored across all production cases; force histories examined over final 800-1200 iterations. Restart from different initial conditions (inviscid vs. medium-mesh restart) compared at α=2.0 deg to assess path dependence.</t>
+          <t>Companion run with outer boundary at 50 c_ref vs. baseline 100 c_ref to assess domain truncation error at M∞=0.85, α=2.0 deg.</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Self-consistency; convergence criteria of ≥3 orders residual drop and ±0.1% force stability</t>
+          <t>Baseline 100 c_ref production domain results</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
-        <is>
-          <t>Standard deviation of force monitors over last 500 iterations</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>σ_CD=0.08 counts; σ_CL=0.03%; restart CD difference ≤0.2 counts; density residual drop 3-4 orders</t>
+          <t>CD change=0.4 counts; CL change=0.06%</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -2255,7 +2255,7 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>Far-Field Domain Size Sensitivity Study</t>
+          <t>Iterative Convergence and Restart Robustness Check</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -2265,22 +2265,27 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Companion run at 50 c_ref outer boundary compared to production 100 c_ref domain to assess domain truncation error contribution.</t>
+          <t>Residuals monitored over all production runs; force monitors assessed over final 500–1200 iterations; restart from different initial conditions (inviscid vs. medium-mesh restart) compared at α=2.0 deg.</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>Production 100 c_ref domain results</t>
+          <t>Convergence criteria: density residual drop ≥3 orders; force stable to ±0.1%; restart difference threshold</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Standard deviation of force monitors over final 500 iterations</t>
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>CD change 0.4 counts; CL change 0.06%</t>
+          <t>σ_CL=0.0003; σ_CD=8.2e-6 (~0.08 counts); restart CD difference ≤0.2 counts; residuals dropped 3–4 orders</t>
         </is>
       </c>
       <c r="I8" s="13" t="inlineStr">
@@ -2434,12 +2439,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Solver identity, build traceability, and version control documented; sufficient for pre-PDR trade study use</t>
+          <t>Solver is a named, version-controlled release with traceable build; input decks archived with timestamps.</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>FUN3D 13.9 is a NASA-developed production CFD solver with documented user guides. The specific executable (fun3d_13.9_skx_dp), build date (2025-12-06), local patch identifier (fb9c3e7), and compiler settings (Intel 2021.6, -O3 -fp-model precise) are recorded. Input decks and mesh files are archived with MD5 checksums and revision identifiers (fun3d.nml rev a12, bcmap.surfmap rev a03). No formal ISO 9001 or DO-178 certification is cited, but traceability is adequate for the stated pre-PDR scope.</t>
+          <t>FUN3D 13.9 is a NASA-developed, publicly released solver with documented user guide. The executable is identified by version (13.9), build date (2025-12-06), local patch (fb9c3e7), and compiler flags (Intel 2021.6, -O3 -fp-model precise). All input decks (fun3d.nml rev a12, bcmap.surfmap rev a03), mesh files (with MD5 checksums), and run cards are archived under a single timestamped directory, providing a reproducible build trace. No explicit regression test suite or ISO quality process is cited beyond the archived inputs and version identification.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2468,12 +2473,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Demonstration of correct order of accuracy on at least one benchmark problem with known solution</t>
+          <t>Code demonstrates expected convergence order on problems with known solutions.</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Two verification exercises were performed. (1) MMS on 2D compressible flow with analytically derived body force: L2(u) slopes 1.98–2.01, L∞(p) 1.72–1.85 across four mesh levels (64² to 512²), consistent with nominal second-order accuracy. (2) Laminar flat-plate Blasius check: c_f within 1.7% of analytical at Rex=1e6. Both checks are documented in Section 5 and Appendix A4/A5, confirming correct discretization and boundary condition behavior on problems with known solutions.</t>
+          <t>Two formal code verification activities are documented. (1) Method of Manufactured Solutions on 2D compressible flow: L2(u) slopes 1.98–2.01 and L∞(p) slopes 1.72–1.85 on uniform triangular meshes from 64² to 512², consistent with nominal second-order accuracy. (2) Laminar flat-plate benchmark: c_f matched Blasius within 1.7% at Rex=1e6. Manufactured solution source term and polynomial definition are recorded in Appendix A4. Both checks confirm discretization and boundary condition implementation behave as expected on problems with analytical solutions.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2502,12 +2507,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Quantified mesh convergence with GCI or equivalent uncertainty estimate for primary QoIs</t>
+          <t>Mesh convergence study with quantified GCI demonstrates numerical errors are acceptable for the decision.</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three systematically refined meshes (8.6M, 17.2M, 34.5M cells, r≈1.26) were run at the primary condition (α=2.0 deg, M∞=0.85). Monotonic convergence observed for CL and CD. Richardson extrapolation applied with observed orders p≈1.95 (drag) and p≈2.08 (lift). GCI (95%) reported as 0.8 counts for drag and 0.6% for lift. Near-wall sensitivity check (y+~0.5) yielded CD change of 0.6 counts. Far-field truncation (50 vs 100 c_ref) added 0.4 counts. Combined numerical uncertainty quoted as 0.9–1.1 counts at 95%. Reported in Sections 4 and 10 and Appendix A2.</t>
+          <t>A three-level mesh family (8.6M, 17.2M, 34.5M cells, refinement ratio r≈1.26) was run at α=2.0 deg, M∞=0.85. CL and CD exhibit monotonic convergence. Richardson extrapolation with observed orders p≈1.95 (drag) and p≈2.08 (lift) yields GCI_drag=0.8 counts and GCI_lift=0.6% at 95% coverage. Additional y+ sensitivity (first cell halved) changed CD by 0.6 counts and CL by 0.1%, confirming wall resolution adequacy. Far-field truncation error separately quantified at 0.4 counts / 0.06% lift from the 50 c_ref sensitivity run.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2529,19 +2534,19 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Residuals drop adequate orders of magnitude and force monitors demonstrate stability</t>
+          <t>Residuals drop sufficient orders; force monitors stable; iterative noise negligible relative to discretization error.</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Density, momentum, and energy residuals dropped 3–4 orders of magnitude across all production cases. Force histories plateaued to within ±0.1% over the final 800–1200 iterations. Standard deviation over last 500 iterations at α=2 deg (fine mesh): σ_CD=0.08 counts (~0.08 counts), σ_CL=0.0003. Late-iteration stalls at α≥3 deg mitigated by CFL reduction from 200 to 120. Restart robustness test showed CD differences ≤0.2 counts. Documented in Sections 3 and 6 and Appendix A3.</t>
+          <t>Density, momentum, and energy residuals decreased by 3–4 orders of magnitude for all production cases. Force histories plateaued to within ±0.1% over the final 800–1200 iterations. Standard deviations over the final 500 iterations: σ_CL=0.0003, σ_CD≈0.08 counts — both negligible compared to the ~1.1-count GCI bound. Restart robustness (inviscid vs. medium-mesh restart) showed CD differences ≤0.2 counts and CL ≤0.05%, demonstrating path independence. At α≥3 deg, late-iteration momentum stalls were mitigated by CFL reduction, documented in Appendix A3.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2570,12 +2575,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Model setup verified through independent checks and documented input traceability</t>
+          <t>Boundary conditions, geometry setup, and post-processing verified through documented checks.</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Boundary conditions are explicitly documented (Appendix A5): far-field p∞, T∞, turbulent eddy viscosity ratio; wall no-slip adiabatic; symmetry plane. Domain size verified via 50 c_ref companion run. Input decks, mesh files (with MD5 checksums), and run cards are archived with date/time stamps enabling reproduction. Geometry cleanup script documented (Glyph, tolerances specified). Turbulence sensitivity to free-stream eddy viscosity ratio (0.01–0.1) performed. No independent peer review by a separate analyst is explicitly documented; setup checks were performed by the same team.</t>
+          <t>Boundary conditions are fully tabulated (Appendix A5): far-field pressure/temperature, no-slip adiabatic walls, symmetry plane, and turbulent eddy viscosity ratio with sensitivity variants. Geometry was cleaned with a reproducible Glyph script (gap healing, watertightness enforcement). Domain size was verified by the 50/100 c_ref comparison. Mesh quality statistics (y+, skewness, aspect ratio) are recorded in Appendix A2. Archived input decks with revision tags (fun3d.nml rev a12, bcmap.surfmap rev a03) support traceability. No independent peer review of model setup is explicitly documented beyond internal group preparation.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2604,12 +2609,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing equations and turbulence model selection justified for the flow regime; known limitations documented</t>
+          <t>Governing equations and turbulence model selection are justified for the flow regime; known limitations documented.</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Steady compressible RANS with SA-RC is identified as a standard choice for attached transonic wing-body flow (Section 11). Rationale for SA-RC (rotation/curvature correction, negative formulation) provided. Operating conditions restricted below buffet onset to remain in the regime where steady RANS is appropriate. Known limitations explicitly stated: no unsteadiness, no aeroelastic deformation, no roughness/support hardware, optimistic drag bias of SA-RC without transition modeling (8–9 count shortfall attributed to model-form bias). Reference to Spalart &amp; Allmaras (1992) provided. Limitations documented in Sections 11 and 12.</t>
+          <t>Steady compressible RANS with Spalart-Allmaras RC is explicitly justified as a standard choice for attached transonic wing-body flow below buffet onset. The report acknowledges model-form limitations: SA-RC optimistic bias on drag (~8–9 counts) at transonic conditions, inability to resolve unsteadiness near buffet, and lack of transition modeling (fully turbulent assumption documented and justified by tripped tunnel model). Limitations of the model for aeroelastic, propulsion, and high-lift configurations are explicitly deferred. Turbulence model reference (Spalart &amp; Allmaras 1992) is cited.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2638,12 +2643,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Operating conditions and geometry inputs traceable to published sources with uncertainties noted where relevant</t>
+          <t>Input data (geometry, operating conditions, turbulence parameters) are well-characterized with sources documented and sensitivity to uncertain inputs assessed.</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Geometry taken from NASA CRM v2.0 IGES (public repository, accessed 2020-06-15); cleanup tolerances documented. Operating conditions (M∞=0.85, Re=5e6/ft, T∞=298 K, p∞=101.3 kPa) derived from the published test matrix. Far-field turbulence ratio sensitivity study (0.01–0.1 eddy viscosity ratio) bounds the impact of free-stream turbulence uncertainty. Transition assumption documented and justified. No facility-specific calibration adjustments applied; this gap is acknowledged. Material properties not applicable (aerodynamics). Input uncertainty not formally propagated via UQ methods but bounded by sensitivity studies.</t>
+          <t>Geometry sourced from NASA CRM v2.0 public CAD (accessed 2020-06-15) with documented cleanup. Operating conditions (M∞=0.85, Re=5e6/ft, T∞=298 K, p∞=101.3 kPa) derive from the published test matrix. Turbulent eddy viscosity ratio sensitivity (0.01 to 0.1) showed CD variation &lt;0.5 counts. Transition assumption (fully turbulent vs. 5% chord) assessed as the dominant input uncertainty (4.2 count drag difference). No facility-specific calibration corrections or support interference adjustments were applied; this limitation is documented. Material properties (adiabatic wall) are standard.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2672,12 +2677,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test article identity and representativeness documented</t>
+          <t>Test dataset is well-characterized and representative of the intended configuration.</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>The comparison uses a publicly available NASA CRM wind-tunnel dataset. The test article is a well-characterized, widely used geometry standard in the aerodynamics community. However, the report does not provide detailed information on the number of test runs, statistical characterization of repeated measurements, surface roughness specifications, or sample-to-sample variability. Mounting hardware and sting interference corrections are noted as not replicated in the simulation. Evidence is adequate for pre-PDR purposes but lacks specimen-level statistical detail.</t>
+          <t>The validation dataset is the publicly available NASA CRM wind-tunnel database, a well-known and widely used aerodynamics benchmark. However, only a single dataset at one Mach-Reynolds condition (M∞=0.85, Re=5e6/ft) was used for direct comparison. No multiple independent test campaigns, no specimen count characterization (this is a wind-tunnel dataset, not a physical sample study), and no statistical characterization of test-to-test repeatability are reported in the evidence corpus. The report explicitly notes that additional datasets at different Re or Mach were not exercised.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2706,12 +2711,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Test conditions and measurement uncertainty documented at a level consistent with the comparison</t>
+          <t>Test conditions are documented and measurement uncertainties are characterized.</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Test conditions (M∞=0.85, Re=5e6/ft, α range) are stated as from the published test matrix. The dataset is publicly available and associated with NASA CRM campaigns. However, the report does not reproduce instrument calibration records, measurement uncertainty quantification for the tunnel data, controlled-environment documentation, or specific test standard (ASTM/ISO) references for the tunnel facility. Tunnel corrections are mentioned as applied to the reported drag (0.02942 after corrections) but correction methodology details are not provided.</t>
+          <t>The public CRM dataset provides tunnel-corrected CL, CD, and CM values at the stated conditions. The report references tunnel corrections applied to CD data. However, no explicit calibration records, measurement uncertainty quantification, or controlled-environment documentation for the wind-tunnel experiment are presented in the evidence corpus — the study relies on a pre-existing public database. Support interference corrections are noted as not accounted for in the simulation side, and surface roughness effects are acknowledged as unmodeled.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2740,12 +2745,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Model boundary conditions match experimental conditions; known differences identified and their impact assessed</t>
+          <t>Simulation input conditions match the experimental conditions with documented differences identified and bounded.</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Nominal flow conditions (M∞, Re, α, T∞, p∞) are matched between simulation and test. Differences are explicitly identified: no mounting hardware, no surface roughness, no facility calibration adjustments. The fully turbulent assumption is justified by the tripped wind-tunnel model, and the impact of transition location (4.2 count CD difference between fully turbulent and 5% chord trip) is quantified. However, formal propagation of experimental measurement uncertainty into model inputs is not performed, and sting/support interference corrections are not replicated. The matching is adequate but not fully quantified.</t>
+          <t>The primary operating conditions (M∞, Re, α sweep) are matched to the published test matrix. The report explicitly identifies and documents known mismatches: no mounting hardware/sting modeled, no surface roughness, no facility-specific calibration adjustments, and transition treatment (fully turbulent vs. tripped model) addressed by sensitivity study. However, no formal propagation of input parameter uncertainty from measurement uncertainties to output uncertainty is performed. The 5% chord transition sensitivity (4.2 drag counts) provides a partial bound on the most influential unmatched input.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2774,12 +2779,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison of primary QoIs against experimental data with uncertainty context</t>
+          <t>Quantitative comparison of simulation outputs to experimental data with error metrics and uncertainty bands reported.</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparisons provided for CL, CD, and CM at α=2.0 deg and across the α sweep. CL offset 1.1% (0.545 vs 0.539), CD shortfall 8.5 counts (discussed in context of RANS bias), CM offset 1.6%. CL slope matches closely (0.096 vs ~0.095/deg). Surface pressure signatures compared qualitatively for shock location. Numerical uncertainty (0.9–1.1 counts drag, ~0.7% lift at 95%) quantified separately from model-form bias. Multiple comparison points (angle sweep) provided. Statistical validation metrics (e.g., correlation coefficients) and formal hypothesis testing not applied. The drag shortfall is acknowledged and contextualized rather than dismissed.</t>
+          <t>Quantitative comparisons are provided for CL, CD, and CM at α=2.0 deg and across the α sweep. CL error=1.1%, CD shortfall=8.5 counts (with physical explanation), CM error=1.6%, CL-α slope comparison (0.096 vs 0.095/deg). Surface pressure signatures compared qualitatively at η≈0.6. Combined numerical uncertainty (grid+iterative+truncation) estimated at 0.9–1.1 drag counts and ~0.7% lift at 95% using quadrature combination. Model-form bias is distinguished from numerical error. Comparison is limited to a single Mach-Reynolds condition; statistical validation metrics (e.g., correlation coefficients) are not computed.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2808,12 +2813,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>QoIs directly address the stated design decision needs and are computable and measurable</t>
+          <t>QoIs (CL, CD, CM) directly address the design decision (cruise drag ranking and margin assessment) and are measurable both computationally and experimentally.</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>The stated QoIs (CL, CD, CM, CL-α slope, surface pressure distribution) directly address the pre-PDR trade study objectives: cruise drag, lift-to-drag ratio, and moment trends. These quantities are both computationally extracted and experimentally measured in the reference dataset. The report explicitly connects the QoIs to the decision context (concept evaluation, margin-setting, drag count resolution of a few counts). Drag uncertainty is bounded and its implication for the decision explicitly discussed. QoI relevance is clearly and thoroughly justified throughout Sections 1, 7, and 11.</t>
+          <t>CL, CD, and CM are the direct outputs needed for cruise drag ranking and lift-to-drag ratio trade studies, matching the stated COU. These quantities are computed by the solver, archived, and compared directly to wind-tunnel measured values from the same geometry. Pitching moment trends inform balance/trim margins. The report is explicit that the QoIs are those relevant to the pre-PDR decision. Surface pressure distributions provide additional resolution of the physical mechanisms. All QoIs are unambiguous and directly measurable on both the computational and experimental sides.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2842,12 +2847,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation conditions (geometry, flow regime, operating point) are representative of the COU; gaps identified</t>
+          <t>Validation conditions (geometry, Mach, Reynolds number, flow regime) match the intended use conditions.</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Validation uses the same CRM geometry, M∞=0.85, Re=5e6/ft, and α range as the intended COU. The physics regime (attached transonic flow below buffet onset) matches the stated operating window. Gaps are explicitly identified: only one Mach/Reynolds combination validated; no aeroelastic deformation, propulsion effects, high-lift devices, or unsteady conditions covered; no roughness or support hardware modeled. These gaps are consciously deferred and documented in Section 12. For the pre-PDR scope, the validation activities are representative of the primary COU but with acknowledged single-dataset limitation.</t>
+          <t>Validation was performed on the exact CRM wing-body geometry at the exact operating condition of interest (M∞=0.85, Re=5e6/ft, α=-1 to 3 deg), which is the COU envelope. The physics regime (attached transonic flow, below buffet) matches the COU constraint. Gaps identified and documented: only a single dataset used (no Re or Mach variation validation), no aeroelastic deformation, no tunnel hardware, no propulsion effects, and unsteadiness near buffet onset not validated. MMS and flat-plate checks provide supporting code-level verification but are not direct application-level validation. The report explicitly acknowledges these as deferred work.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -3032,7 +3037,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The evidence collectively supports acceptance of the FUN3D 13.9 SA-RC RANS model for the stated COU of pre-PDR concept evaluation and margin-setting at transonic cruise conditions on the CRM wing-body. Mesh convergence is demonstrated with quantified GCI (drag ~0.8 counts, lift ~0.6% at 95%), numerical verification is confirmed via MMS and flat-plate benchmarks, and iterative convergence is robust. Lift slope and pitching moment trends agree closely with the CRM wind-tunnel dataset; the 8–9 count drag shortfall is acknowledged, contextualized as consistent with known RANS bias and missing facility effects, and is acceptable for the stated decision fidelity (concept ranking, a-few-drag-count margins). Sensitivity studies bound the influence of free-stream turbulence, far-field size, and transition assumption. Model limitations (no aeroelastic coupling, no unsteadiness near buffet, single validation dataset) are explicitly documented and accepted as consistent with pre-PDR scope. Accepted with the recognized caveat that tighter absolute drag accuracy (≤5 counts) for downstream phases will require expanded validation, transition modeling, and potentially higher-fidelity turbulence closure.</t>
+          <t>The evidence supports use of the FUN3D 13.9 RANS predictions for pre-PDR concept evaluation and drag margin ranking in the specified transonic cruise window (M∞=0.85, Re=5e6/ft, α=-1 to 3 deg). Mesh convergence with quantified GCI (~0.8 counts drag, 95%), MMS-confirmed second-order accuracy, stable iterative convergence, and documented sensitivity studies collectively establish numerical credibility. Trends in CL-α slope and pitching moment agree well with the CRM public dataset; the 8–9 count drag shortfall is physically explained (absence of tunnel corrections, roughness, support interference) and is consistent with known RANS behavior, providing a conservative bound for design decisions. Conditions on accepted use: (1) absolute drag predictions carry a ~8–9 count optimistic bias that must be acknowledged in trade study interpretation; (2) for downstream phases requiring drag accuracy ≤5 counts, the comparison dataset should be expanded to multiple Re/Mach conditions, transition modeling should be refined, and a higher-fidelity turbulence closure or unsteady approach should be considered; (3) aeroelastic, propulsion-airframe, and high-lift configurations are outside the validated envelope and require separate assessment.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
